--- a/data/ams_weekly_data/White_Mulberry/ads_report_week33.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week33.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SP" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SD" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SB" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="SP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="SD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="SB" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,16 +19,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -39,7 +36,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -47,21 +44,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -431,42 +419,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
@@ -1527,7 +1515,7 @@
         <v>239</v>
       </c>
       <c r="F39" t="n">
-        <v>124188</v>
+        <v>124186</v>
       </c>
       <c r="G39" t="n">
         <v>17868.5</v>
@@ -1614,10 +1602,10 @@
         <v>17149</v>
       </c>
       <c r="G42" t="n">
-        <v>59010.73</v>
+        <v>56809.2</v>
       </c>
       <c r="H42" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="43">
@@ -1639,7 +1627,7 @@
         <v>83</v>
       </c>
       <c r="F43" t="n">
-        <v>5821</v>
+        <v>5819</v>
       </c>
       <c r="G43" t="n">
         <v>2329.66</v>
@@ -2367,7 +2355,7 @@
         <v>313</v>
       </c>
       <c r="F69" t="n">
-        <v>17446</v>
+        <v>17444</v>
       </c>
       <c r="G69" t="n">
         <v>21114.42</v>
@@ -2591,7 +2579,7 @@
         <v>222</v>
       </c>
       <c r="F77" t="n">
-        <v>59366</v>
+        <v>59365</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2846,10 +2834,10 @@
         <v>14231</v>
       </c>
       <c r="G86" t="n">
-        <v>25350.66</v>
+        <v>27680.32</v>
       </c>
       <c r="H86" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="87">
@@ -3011,7 +2999,7 @@
         <v>52</v>
       </c>
       <c r="F92" t="n">
-        <v>6644</v>
+        <v>6643</v>
       </c>
       <c r="G92" t="n">
         <v>1600.9</v>
@@ -3098,10 +3086,10 @@
         <v>13797</v>
       </c>
       <c r="G95" t="n">
-        <v>1863.56</v>
+        <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -3315,42 +3303,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
@@ -4239,47 +4227,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
@@ -4340,10 +4328,10 @@
         <v>607.25</v>
       </c>
       <c r="G3" t="n">
-        <v>13896.62</v>
+        <v>6948.31</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>

--- a/data/ams_weekly_data/White_Mulberry/ads_report_week33.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week33.xlsx
@@ -1518,10 +1518,10 @@
         <v>124186</v>
       </c>
       <c r="G39" t="n">
-        <v>17868.5</v>
+        <v>25155.78</v>
       </c>
       <c r="H39" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40">
@@ -4223,7 +4223,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4315,23 +4315,23 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>5776</v>
+        <v>2888</v>
       </c>
       <c r="E3" t="n">
-        <v>224</v>
+        <v>112</v>
       </c>
       <c r="F3" t="n">
-        <v>607.25</v>
+        <v>303.625</v>
       </c>
       <c r="G3" t="n">
-        <v>6948.31</v>
+        <v>3474.155</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Camb-SP-Zshape-B0CPFS24ML- SBV- Phrase</t>
+          <t>Camb-SB-Multiple Asin- Product collection- exact /Reach</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -4352,16 +4352,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>66670</v>
+        <v>2888</v>
       </c>
       <c r="E4" t="n">
-        <v>204</v>
+        <v>112</v>
       </c>
       <c r="F4" t="n">
-        <v>2066</v>
+        <v>303.625</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>3474.155</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -4376,22 +4376,22 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SB-L shape-Multi Asin- KT- phrase</t>
+          <t>Camb-SP-Zshape-B0CPFS24ML- SBV- Phrase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>8958</v>
+        <v>66670</v>
       </c>
       <c r="E5" t="n">
-        <v>58</v>
+        <v>204</v>
       </c>
       <c r="F5" t="n">
-        <v>432.3375</v>
+        <v>2066</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -4414,7 +4414,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B0BFVNS8HS</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -4447,7 +4447,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0BFVNS8HS</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -4508,28 +4508,28 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>WM- SBV- Monitor Arm- Product Collection- Phrase</t>
+          <t>SB-L shape-Multi Asin- KT- phrase</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>23419</v>
+        <v>8958</v>
       </c>
       <c r="E9" t="n">
-        <v>145</v>
+        <v>58</v>
       </c>
       <c r="F9" t="n">
-        <v>2693.313808066428</v>
+        <v>432.3375</v>
       </c>
       <c r="G9" t="n">
-        <v>14156.7681124154</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -4546,23 +4546,23 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3698</v>
+        <v>23419</v>
       </c>
       <c r="E10" t="n">
-        <v>23</v>
+        <v>145</v>
       </c>
       <c r="F10" t="n">
-        <v>425.3313045759992</v>
+        <v>2693.313808066428</v>
       </c>
       <c r="G10" t="n">
-        <v>2235.653577314239</v>
+        <v>14156.7681124154</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -4579,23 +4579,23 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10797</v>
+        <v>3698</v>
       </c>
       <c r="E11" t="n">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="F11" t="n">
-        <v>1241.664887357573</v>
+        <v>425.3313045759992</v>
       </c>
       <c r="G11" t="n">
-        <v>6526.51831027036</v>
+        <v>2235.653577314239</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -4607,28 +4607,28 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
+          <t>WM- SBV- Monitor Arm- Product Collection- Phrase</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>10797</v>
       </c>
       <c r="E12" t="n">
+        <v>67</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1241.664887357573</v>
+      </c>
+      <c r="G12" t="n">
+        <v>6526.51831027036</v>
+      </c>
+      <c r="H12" t="n">
         <v>3</v>
-      </c>
-      <c r="F12" t="n">
-        <v>38.43905909435872</v>
-      </c>
-      <c r="G12" t="n">
-        <v>2201.53</v>
-      </c>
-      <c r="H12" t="n">
-        <v>1</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -4645,20 +4645,20 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>167</v>
+        <v>99</v>
       </c>
       <c r="E13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F13" t="n">
-        <v>65.09094090564129</v>
+        <v>38.43905909435872</v>
       </c>
       <c r="G13" t="n">
-        <v>3727.97</v>
+        <v>2201.53</v>
       </c>
       <c r="H13" t="n">
         <v>1</v>
@@ -4673,28 +4673,28 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- BM</t>
+          <t>WM-SB-Monitor Arms-Branded</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4853</v>
+        <v>167</v>
       </c>
       <c r="E14" t="n">
-        <v>57</v>
+        <v>5</v>
       </c>
       <c r="F14" t="n">
-        <v>876.66</v>
+        <v>65.09094090564129</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>3727.97</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
+          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- BM</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -4715,19 +4715,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>20743</v>
+        <v>4853</v>
       </c>
       <c r="E15" t="n">
-        <v>194</v>
+        <v>57</v>
       </c>
       <c r="F15" t="n">
-        <v>2901.52244673531</v>
+        <v>876.66</v>
       </c>
       <c r="G15" t="n">
-        <v>4659.32</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -4744,23 +4744,23 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0DP2VVRND</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>7919</v>
+        <v>20743</v>
       </c>
       <c r="E16" t="n">
-        <v>74</v>
+        <v>194</v>
       </c>
       <c r="F16" t="n">
-        <v>1107.72755326469</v>
+        <v>2901.52244673531</v>
       </c>
       <c r="G16" t="n">
-        <v>1778.81</v>
+        <v>4659.32</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -4772,30 +4772,63 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
+          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>B0DP2VVRND</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>7919</v>
+      </c>
+      <c r="E17" t="n">
+        <v>74</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1107.72755326469</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1778.81</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>White Mulberry Monitor Arm-B0DB5VG39T-CT-SBV</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>B0DB5VG39T</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D18" t="n">
         <v>8637</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E18" t="n">
         <v>113</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F18" t="n">
         <v>1000.94</v>
       </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="inlineStr">
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="inlineStr">
         <is>
           <t>White Mulberry</t>
         </is>
